--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55F9AC2-986F-4CFB-B3CF-80ACEDA8D76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93B1542-8D10-46A3-9104-2DFBA5B0BF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,8 +24,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>fangmenglu</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{279665AC-3B9C-4E41-8A7C-7EC5099B4FAA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>ex-hard:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+runtime不会用到，编辑器中会使用，ge编辑时会展示cue名字方便查找使用</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -39,6 +75,15 @@
     <t>desc</t>
   </si>
   <si>
+    <t>required_tag</t>
+  </si>
+  <si>
+    <t>immunity_tag</t>
+  </si>
+  <si>
+    <t>cue_logic</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -48,26 +93,72 @@
     <t>string</t>
   </si>
   <si>
+    <t>(list#sep=;),int</t>
+  </si>
+  <si>
+    <t>CueLogic</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
-    <t>cue作用描述，以及参数的使用</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cue名字：runtime不会用到，编辑器中会使用，ge编辑时会展示cue名字方便查找使用</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>cue名字</t>
+  </si>
+  <si>
+    <t>作用描述</t>
+  </si>
+  <si>
+    <t>需要的标签</t>
+  </si>
+  <si>
+    <t>免疫的标签</t>
+  </si>
+  <si>
+    <t>cue逻辑：支持多态，添加新CueLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
   </si>
   <si>
     <t>打印日志</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于打印日志</t>
+  </si>
+  <si>
+    <t>100;1001</t>
+  </si>
+  <si>
+    <t>200;2001</t>
+  </si>
+  <si>
+    <t>GameplayCueLog</t>
+  </si>
+  <si>
+    <t>testMessageA</t>
+  </si>
+  <si>
+    <t>打印持续日志</t>
+  </si>
+  <si>
+    <t>用于打印持续日志</t>
+  </si>
+  <si>
+    <t>100;1002;2002;2005</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CueLoging</t>
+  </si>
+  <si>
+    <t>testValue2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,14 +171,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -99,7 +182,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -107,6 +190,86 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -114,18 +277,53 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{55324ADC-B395-4A2E-867E-64A197BD9EA7}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -402,16 +600,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="26.5546875" customWidth="1"/>
-    <col min="4" max="4" width="26.77734375" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1" style="3"/>
+    <col min="4" max="6" width="14.44140625" customWidth="1" style="3"/>
+    <col min="7" max="7" width="16.77734375" customWidth="1" style="3"/>
+    <col min="8" max="8" width="15" customWidth="1" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -424,153 +623,282 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="9"/>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="12"/>
+    </row>
+    <row r="3" ht="14.4">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="15"/>
+    </row>
+    <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1.5499999523162842</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="C6" s="1"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8">
       <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14">
       <c r="B14" s="1"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15">
       <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16">
       <c r="B16" s="1"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17">
       <c r="B17" s="1"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18">
       <c r="B18" s="1"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19">
       <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20">
       <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25">
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
+  <mergeCells>
+    <mergeCell ref="G1:T1"/>
+    <mergeCell ref="G2:T2"/>
+    <mergeCell ref="G3:T3"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -151,6 +151,21 @@
   </si>
   <si>
     <t>testValue2</t>
+  </si>
+  <si>
+    <t>测试3</t>
+  </si>
+  <si>
+    <t>看看拉屎都</t>
+  </si>
+  <si>
+    <t>200;2005</t>
+  </si>
+  <si>
+    <t>3002;2006;2003;2001;1002;100;1001</t>
+  </si>
+  <si>
+    <t>卧槽</t>
   </si>
 </sst>
 </file>
@@ -770,10 +785,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="1"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="B6" s="2">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="4"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93B1542-8D10-46A3-9104-2DFBA5B0BF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ED3283-04C5-4C8C-9D22-EF0E424A9A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -81,9 +81,6 @@
     <t>immunity_tag</t>
   </si>
   <si>
-    <t>cue_logic</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -166,14 +163,17 @@
   </si>
   <si>
     <t>卧槽</t>
+  </si>
+  <si>
+    <t>cueLogic</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +187,21 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -293,52 +308,52 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -619,13 +634,13 @@
   <dimension ref="A1:T26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" customWidth="1" style="3"/>
-    <col min="4" max="6" width="14.44140625" customWidth="1" style="3"/>
-    <col min="7" max="7" width="16.77734375" customWidth="1" style="3"/>
-    <col min="8" max="8" width="15" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.21875" style="3" customWidth="1"/>
+    <col min="4" max="6" width="14.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,7 +660,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
@@ -661,27 +676,27 @@
       <c r="S1" s="8"/>
       <c r="T1" s="9"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="10" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>11</v>
       </c>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -697,27 +712,27 @@
       <c r="S2" s="11"/>
       <c r="T2" s="12"/>
     </row>
-    <row r="3" ht="14.4">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
@@ -733,207 +748,206 @@
       <c r="S3" s="14"/>
       <c r="T3" s="15"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="I5" s="3">
         <v>1.5499999523162842</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="I6" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
-    <row r="17">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
     </row>
-    <row r="20">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
     </row>
-    <row r="26">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="G1:T1"/>
     <mergeCell ref="G2:T2"/>
     <mergeCell ref="G3:T3"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ED3283-04C5-4C8C-9D22-EF0E424A9A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7243A022-D1AF-4A7B-A3A3-5C7B8D3D31B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -61,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -126,9 +129,6 @@
     <t>200;2001</t>
   </si>
   <si>
-    <t>GameplayCueLog</t>
-  </si>
-  <si>
     <t>testMessageA</t>
   </si>
   <si>
@@ -144,9 +144,6 @@
     <t/>
   </si>
   <si>
-    <t>CueLoging</t>
-  </si>
-  <si>
     <t>testValue2</t>
   </si>
   <si>
@@ -166,6 +163,10 @@
   </si>
   <si>
     <t>cueLogic</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CueLogging</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -660,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
@@ -765,11 +766,14 @@
       <c r="F4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
+      <c r="I4">
+        <v>2.5</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -778,22 +782,22 @@
         <v>1002</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="I5" s="3">
         <v>1.5499999523162842</v>
@@ -804,22 +808,22 @@
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="G6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="I6" s="2">
         <v>30</v>
@@ -831,6 +835,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7243A022-D1AF-4A7B-A3A3-5C7B8D3D31B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22011ED-4658-4886-BF53-2435C1EDE2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -72,18 +72,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>required_tag</t>
-  </si>
-  <si>
-    <t>immunity_tag</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -162,11 +150,31 @@
     <t>卧槽</t>
   </si>
   <si>
-    <t>cueLogic</t>
+    <t>CueLogging</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>CueLogging</t>
+    <t>ID</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequiredTag</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImmunityTag</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CueLogic</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -646,22 +654,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
@@ -679,25 +687,25 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>10</v>
       </c>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -715,25 +723,25 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>16</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
@@ -755,22 +763,22 @@
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="I4">
         <v>2.5</v>
@@ -782,22 +790,22 @@
         <v>1002</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="3">
         <v>1.5499999523162842</v>
@@ -808,22 +816,22 @@
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="I6" s="2">
         <v>30</v>
